--- a/blocks_final_express.xlsx
+++ b/blocks_final_express.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Backups\All Files\Genel\Is\2022\Upwork\LabX\studies\materials\drivingSimulator\repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D613608-A9F2-4027-92AD-B003ED6BAFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F36B8D6-6CB7-4E0A-8DC7-0360305B00B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="1290" windowWidth="25875" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
   <si>
     <t>current_font</t>
   </si>
@@ -130,6 +130,18 @@
   </si>
   <si>
     <t>./instructions_pilot/clutterlex_driving_training.png</t>
+  </si>
+  <si>
+    <t>scoreRegistry</t>
+  </si>
+  <si>
+    <t>lexical_only</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>driving_lexical</t>
   </si>
 </sst>
 </file>
@@ -447,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
@@ -456,7 +468,7 @@
     <col min="8" max="8" width="55.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,8 +505,11 @@
       <c r="L1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -531,8 +546,11 @@
       <c r="L2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -569,8 +587,11 @@
       <c r="L3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -607,8 +628,11 @@
       <c r="L4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -645,8 +669,11 @@
       <c r="L5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -660,10 +687,10 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
@@ -683,8 +710,11 @@
       <c r="L6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -698,10 +728,10 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
@@ -721,8 +751,11 @@
       <c r="L7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G8" t="s">
         <v>9</v>
@@ -759,8 +792,11 @@
       <c r="L8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -774,10 +810,10 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G9" t="s">
         <v>9</v>
@@ -797,8 +833,11 @@
       <c r="L9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -812,10 +851,10 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G10" t="s">
         <v>9</v>
@@ -834,6 +873,9 @@
       </c>
       <c r="L10" t="b">
         <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
